--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:09:28+00:00</t>
+    <t>2023-06-12T13:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -236,10 +236,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from LOINC" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from ARV Treatment Me" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,13 +99,10 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>45260-7</t>
-  </si>
-  <si>
-    <t>HIV ART medication</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -114,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://loinc.org</t>
+    <t>http://openhie.org/fhir/training-solution-1/CodeSystem/cs-arvtreatment-activity-type</t>
   </si>
 </sst>
 </file>
@@ -397,32 +394,26 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-arvtreatment-activity-type.xlsx
+++ b/ValueSet-vs-arvtreatment-activity-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
